--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -7740,6 +7740,9 @@
       <c r="AD46" t="n">
         <v>19327</v>
       </c>
+      <c r="AE46" t="n">
+        <v>19570</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -9783,6 +9786,9 @@
       <c r="AD68" t="n">
         <v>34353</v>
       </c>
+      <c r="AE68" t="n">
+        <v>44446</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -10128,6 +10134,9 @@
       <c r="AD72" t="n">
         <v>13067</v>
       </c>
+      <c r="AE72" t="n">
+        <v>13868</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -10945,6 +10954,9 @@
       </c>
       <c r="AD80" t="n">
         <v>17223</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>17876</v>
       </c>
     </row>
     <row r="81">
@@ -62194,6 +62206,9 @@
       <c r="AC18" t="n">
         <v>34353</v>
       </c>
+      <c r="AD18" t="n">
+        <v>44446</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -9080,6 +9080,9 @@
       <c r="AD62" t="n">
         <v>16778</v>
       </c>
+      <c r="AE62" t="n">
+        <v>31340</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -9278,6 +9281,9 @@
       <c r="AD64" t="n">
         <v>10768</v>
       </c>
+      <c r="AE64" t="n">
+        <v>19256</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -10573,6 +10579,9 @@
       <c r="AD77" t="n">
         <v>46258</v>
       </c>
+      <c r="AE77" t="n">
+        <v>48705</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -18912,6 +18921,9 @@
       <c r="AD171" t="n">
         <v>4774</v>
       </c>
+      <c r="AE171" t="n">
+        <v>19256</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -18983,6 +18995,9 @@
       <c r="AD172" t="n">
         <v>8486</v>
       </c>
+      <c r="AE172" t="n">
+        <v>19256</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -19212,6 +19227,9 @@
       </c>
       <c r="AD175" t="n">
         <v>6962</v>
+      </c>
+      <c r="AE175" t="n">
+        <v>48705</v>
       </c>
     </row>
     <row r="176">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -9080,9 +9080,6 @@
       <c r="AD62" t="n">
         <v>16778</v>
       </c>
-      <c r="AE62" t="n">
-        <v>31340</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -9219,9 +9216,6 @@
       <c r="AD63" t="n">
         <v>12300</v>
       </c>
-      <c r="AE63" t="n">
-        <v>31340</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -9281,9 +9275,6 @@
       <c r="AD64" t="n">
         <v>10768</v>
       </c>
-      <c r="AE64" t="n">
-        <v>19256</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -10579,9 +10570,6 @@
       <c r="AD77" t="n">
         <v>46258</v>
       </c>
-      <c r="AE77" t="n">
-        <v>48705</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -18774,9 +18762,6 @@
       <c r="AD170" t="n">
         <v>7645</v>
       </c>
-      <c r="AE170" t="n">
-        <v>19256</v>
-      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -18921,9 +18906,6 @@
       <c r="AD171" t="n">
         <v>4774</v>
       </c>
-      <c r="AE171" t="n">
-        <v>19256</v>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -18995,9 +18977,6 @@
       <c r="AD172" t="n">
         <v>8486</v>
       </c>
-      <c r="AE172" t="n">
-        <v>19256</v>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -19227,9 +19206,6 @@
       </c>
       <c r="AD175" t="n">
         <v>6962</v>
-      </c>
-      <c r="AE175" t="n">
-        <v>48705</v>
       </c>
     </row>
     <row r="176">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -5940,6 +5940,9 @@
       <c r="AD25" t="n">
         <v>31203</v>
       </c>
+      <c r="AE25" t="n">
+        <v>33686</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9988,6 +9991,9 @@
       </c>
       <c r="AD70" t="n">
         <v>43654</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>45299</v>
       </c>
     </row>
     <row r="71">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -8525,6 +8525,9 @@
       <c r="AD56" t="n">
         <v>45055</v>
       </c>
+      <c r="AE56" t="n">
+        <v>47508</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -14483,6 +14483,9 @@
       <c r="AD118" t="n">
         <v>33050</v>
       </c>
+      <c r="AE118" t="n">
+        <v>34003</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -14585,6 +14588,9 @@
       <c r="AD119" t="n">
         <v>4699</v>
       </c>
+      <c r="AE119" t="n">
+        <v>5279</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -14656,6 +14662,9 @@
       <c r="AD120" t="n">
         <v>30049</v>
       </c>
+      <c r="AE120" t="n">
+        <v>27883</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -14976,6 +14985,9 @@
       <c r="AC124" t="n">
         <v>19748</v>
       </c>
+      <c r="AE124" t="n">
+        <v>5026</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -15313,6 +15325,9 @@
       </c>
       <c r="AD128" t="n">
         <v>20007</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>19814</v>
       </c>
     </row>
     <row r="129">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -8629,6 +8629,9 @@
       <c r="AD57" t="n">
         <v>28474</v>
       </c>
+      <c r="AE57" t="n">
+        <v>30341</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -15738,6 +15741,9 @@
       <c r="AC133" t="n">
         <v>7533</v>
       </c>
+      <c r="AE133" t="n">
+        <v>9602</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -18510,6 +18516,9 @@
       <c r="AD167" t="n">
         <v>73253</v>
       </c>
+      <c r="AE167" t="n">
+        <v>77382</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -23073,6 +23082,9 @@
       </c>
       <c r="AD273" t="n">
         <v>23045</v>
+      </c>
+      <c r="AE273" t="n">
+        <v>15497</v>
       </c>
     </row>
     <row r="274">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -3241,7 +3241,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Canceled</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>Canceled</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9653,6 +9653,11 @@
       </c>
       <c r="AD67" t="n">
         <v>40241</v>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="68">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -8903,6 +8903,9 @@
       <c r="AD60" t="n">
         <v>17697</v>
       </c>
+      <c r="AE60" t="n">
+        <v>11230</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -21803,6 +21806,9 @@
       <c r="AD221" t="n">
         <v>21403</v>
       </c>
+      <c r="AE221" t="n">
+        <v>16144</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -22791,6 +22797,9 @@
       <c r="AD261" t="n">
         <v>20912</v>
       </c>
+      <c r="AE261" t="n">
+        <v>23645</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -23115,6 +23124,9 @@
       </c>
       <c r="AD274" t="n">
         <v>22779</v>
+      </c>
+      <c r="AE274" t="n">
+        <v>26867</v>
       </c>
     </row>
     <row r="275">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -26268,7 +26268,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Francfort</t>
+          <t>Hambourg</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -16332,6 +16332,9 @@
       <c r="AD141" t="n">
         <v>15569</v>
       </c>
+      <c r="AE141" t="n">
+        <v>3563</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -25068,6 +25071,9 @@
       <c r="AD354" t="n">
         <v>16600</v>
       </c>
+      <c r="AE354" t="n">
+        <v>18607</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -26455,6 +26461,9 @@
       </c>
       <c r="AD411" t="n">
         <v>13798</v>
+      </c>
+      <c r="AE411" t="n">
+        <v>5138</v>
       </c>
     </row>
     <row r="412">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -10347,6 +10347,9 @@
       <c r="AD74" t="n">
         <v>32963</v>
       </c>
+      <c r="AE74" t="n">
+        <v>36259</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -17990,6 +17990,9 @@
       <c r="AD160" t="n">
         <v>18839</v>
       </c>
+      <c r="AE160" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -25253,6 +25253,9 @@
           <t>★</t>
         </is>
       </c>
+      <c r="AE361" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -739,6 +739,9 @@
       <c r="AB9" t="n">
         <v>18157</v>
       </c>
+      <c r="AC9" t="n">
+        <v>20316</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -765,6 +768,9 @@
       <c r="AB10" t="n">
         <v>7142</v>
       </c>
+      <c r="AC10" t="n">
+        <v>8491</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -866,6 +872,9 @@
       <c r="AB14" t="n">
         <v>13543</v>
       </c>
+      <c r="AC14" t="n">
+        <v>13543</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -943,6 +952,9 @@
       </c>
       <c r="AB17" t="n">
         <v>24703</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>27921</v>
       </c>
     </row>
     <row r="18">
@@ -1862,7 +1874,10 @@
         </is>
       </c>
       <c r="AB29" t="n">
-        <v>11795</v>
+        <v>3160</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3790</v>
       </c>
     </row>
     <row r="30">
@@ -1881,9 +1896,6 @@
           <t>St. Jude Rock 'n' Roll Series Nashville</t>
         </is>
       </c>
-      <c r="AB30" t="n">
-        <v>10776</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1913,6 +1925,9 @@
       <c r="AB31" t="n">
         <v>46706</v>
       </c>
+      <c r="AC31" t="n">
+        <v>45578</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1953,6 +1968,9 @@
       <c r="AB33" t="n">
         <v>20531</v>
       </c>
+      <c r="AC33" t="n">
+        <v>24377</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1970,8 +1988,17 @@
           <t>IU Health 500 Festival Mini-Marathon</t>
         </is>
       </c>
+      <c r="Z34" t="n">
+        <v>14234</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>15925</v>
+      </c>
       <c r="AB34" t="n">
-        <v>17697</v>
+        <v>17593</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>22323</v>
       </c>
     </row>
     <row r="35">
@@ -1993,6 +2020,9 @@
       <c r="AB35" t="n">
         <v>17222</v>
       </c>
+      <c r="AC35" t="n">
+        <v>17515</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2073,6 +2103,9 @@
       <c r="AB39" t="n">
         <v>21011</v>
       </c>
+      <c r="AC39" t="n">
+        <v>20665</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2093,6 +2126,9 @@
       <c r="AB40" t="n">
         <v>11218</v>
       </c>
+      <c r="AC40" t="n">
+        <v>11462</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2124,6 +2160,9 @@
       </c>
       <c r="AB41" t="n">
         <v>46258</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>48719</v>
       </c>
     </row>
     <row r="42">
@@ -3190,6 +3229,9 @@
       <c r="AB17" t="n">
         <v>18508</v>
       </c>
+      <c r="AC17" t="n">
+        <v>22472</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3244,6 +3286,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC19" t="n">
+        <v>18526</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3269,6 +3314,9 @@
       </c>
       <c r="AB20" t="n">
         <v>29363</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>28949</v>
       </c>
     </row>
     <row r="21">
@@ -7817,6 +7865,9 @@
       <c r="AD47" t="n">
         <v>18157</v>
       </c>
+      <c r="AE47" t="n">
+        <v>20316</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7984,7 +8035,10 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>11795</v>
+        <v>3160</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>3790</v>
       </c>
     </row>
     <row r="51">
@@ -8156,9 +8210,6 @@
       <c r="AA52" t="n">
         <v>12359</v>
       </c>
-      <c r="AD52" t="n">
-        <v>10776</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -8374,6 +8425,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AE54" t="n">
+        <v>18526</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -8430,6 +8484,9 @@
       <c r="AD55" t="n">
         <v>46706</v>
       </c>
+      <c r="AE55" t="n">
+        <v>45578</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -8767,6 +8824,9 @@
       <c r="AD58" t="n">
         <v>20531</v>
       </c>
+      <c r="AE58" t="n">
+        <v>24377</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -8856,6 +8916,9 @@
       <c r="AD59" t="n">
         <v>18549</v>
       </c>
+      <c r="AE59" t="n">
+        <v>22472</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -8900,11 +8963,17 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AB60" t="n">
+        <v>14234</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>15925</v>
+      </c>
       <c r="AD60" t="n">
-        <v>17697</v>
+        <v>17593</v>
       </c>
       <c r="AE60" t="n">
-        <v>11230</v>
+        <v>22323</v>
       </c>
     </row>
     <row r="61">
@@ -9003,6 +9072,9 @@
       <c r="AD61" t="n">
         <v>17222</v>
       </c>
+      <c r="AE61" t="n">
+        <v>17515</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -9517,6 +9589,9 @@
       <c r="AD66" t="n">
         <v>7142</v>
       </c>
+      <c r="AE66" t="n">
+        <v>8491</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -9934,6 +10009,9 @@
       <c r="AD69" t="n">
         <v>13543</v>
       </c>
+      <c r="AE69" t="n">
+        <v>13543</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -10047,6 +10125,9 @@
       <c r="AD71" t="n">
         <v>21011</v>
       </c>
+      <c r="AE71" t="n">
+        <v>20665</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -10249,6 +10330,9 @@
       <c r="AD73" t="n">
         <v>11218</v>
       </c>
+      <c r="AE73" t="n">
+        <v>11462</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -10410,6 +10494,9 @@
       <c r="AD75" t="n">
         <v>29363</v>
       </c>
+      <c r="AE75" t="n">
+        <v>28949</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -10593,6 +10680,9 @@
       <c r="AD77" t="n">
         <v>46258</v>
       </c>
+      <c r="AE77" t="n">
+        <v>48719</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -10849,6 +10939,12 @@
       </c>
       <c r="AC79" t="n">
         <v>22903</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>24703</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>27921</v>
       </c>
     </row>
     <row r="80">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -10780,9 +10780,6 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T78" t="n">
-        <v>20000</v>
-      </c>
       <c r="Y78" t="inlineStr">
         <is>
           <t>-</t>
@@ -11149,9 +11146,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA81" t="n">
-        <v>13500</v>
-      </c>
       <c r="AB81" t="n">
         <v>12201</v>
       </c>
@@ -14675,9 +14669,6 @@
       <c r="W119" t="n">
         <v>5829</v>
       </c>
-      <c r="X119" t="n">
-        <v>31325</v>
-      </c>
       <c r="Y119" t="inlineStr">
         <is>
           <t>-</t>
@@ -15273,9 +15264,6 @@
       <c r="W126" t="n">
         <v>1179</v>
       </c>
-      <c r="X126" t="n">
-        <v>18852</v>
-      </c>
       <c r="AA126" t="n">
         <v>939</v>
       </c>
@@ -15620,9 +15608,6 @@
       <c r="W130" t="n">
         <v>2549</v>
       </c>
-      <c r="X130" t="n">
-        <v>13914</v>
-      </c>
       <c r="AA130" t="n">
         <v>2766</v>
       </c>
@@ -15930,9 +15915,6 @@
       <c r="W134" t="n">
         <v>3067</v>
       </c>
-      <c r="X134" t="n">
-        <v>18806</v>
-      </c>
       <c r="Y134" t="inlineStr">
         <is>
           <t>-</t>
@@ -16138,9 +16120,6 @@
       <c r="AC137" t="n">
         <v>13767</v>
       </c>
-      <c r="AD137" t="n">
-        <v>17278</v>
-      </c>
       <c r="AE137" t="n">
         <v>2527</v>
       </c>
@@ -16220,12 +16199,6 @@
       <c r="V138" t="n">
         <v>4250</v>
       </c>
-      <c r="W138" t="n">
-        <v>4000</v>
-      </c>
-      <c r="X138" t="n">
-        <v>15382</v>
-      </c>
       <c r="Y138" t="inlineStr">
         <is>
           <t>-</t>
@@ -16428,9 +16401,6 @@
       <c r="AC141" t="n">
         <v>16080</v>
       </c>
-      <c r="AD141" t="n">
-        <v>15569</v>
-      </c>
       <c r="AE141" t="n">
         <v>3563</v>
       </c>
@@ -16688,9 +16658,6 @@
       <c r="W144" t="n">
         <v>1435</v>
       </c>
-      <c r="X144" t="n">
-        <v>19965</v>
-      </c>
       <c r="Z144" t="n">
         <v>339</v>
       </c>
@@ -16878,9 +16845,6 @@
       <c r="W146" t="n">
         <v>3214</v>
       </c>
-      <c r="X146" t="n">
-        <v>12530</v>
-      </c>
       <c r="Y146" t="inlineStr">
         <is>
           <t>-</t>
@@ -22315,9 +22279,6 @@
           <t>Chengdu World heritage Marathon</t>
         </is>
       </c>
-      <c r="AD238" t="n">
-        <v>29050</v>
-      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -22340,9 +22301,6 @@
           <t>Chengdu World heritage Marathon</t>
         </is>
       </c>
-      <c r="AD239" t="n">
-        <v>29050</v>
-      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -22365,9 +22323,6 @@
           <t>Two Oceans Marathon</t>
         </is>
       </c>
-      <c r="AD240" t="n">
-        <v>28858</v>
-      </c>
       <c r="AE240" t="n">
         <v>14687</v>
       </c>
@@ -22393,9 +22348,6 @@
           <t>Two Oceans Marathon</t>
         </is>
       </c>
-      <c r="AD241" t="n">
-        <v>28858</v>
-      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -22468,9 +22420,6 @@
           <t>Wuxi Marathon</t>
         </is>
       </c>
-      <c r="AD244" t="n">
-        <v>27390</v>
-      </c>
       <c r="AE244" t="n">
         <v>24088</v>
       </c>
@@ -22496,9 +22445,6 @@
           <t>Wuxi Marathon</t>
         </is>
       </c>
-      <c r="AD245" t="n">
-        <v>27390</v>
-      </c>
       <c r="AE245" t="n">
         <v>8498</v>
       </c>
@@ -23346,9 +23292,6 @@
           <t>Behobia San Sebastian</t>
         </is>
       </c>
-      <c r="AD279" t="n">
-        <v>22410</v>
-      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -23371,9 +23314,6 @@
           <t>Behobia San Sebastian</t>
         </is>
       </c>
-      <c r="AD280" t="n">
-        <v>22410</v>
-      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -23396,9 +23336,6 @@
           <t>Marathon International du Beaujolais</t>
         </is>
       </c>
-      <c r="AD281" t="n">
-        <v>22171</v>
-      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -23421,9 +23358,6 @@
           <t>Marathon International du Beaujolais</t>
         </is>
       </c>
-      <c r="AD282" t="n">
-        <v>22171</v>
-      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -23693,9 +23627,6 @@
           <t>Semi &amp; 10km de Bordeaux</t>
         </is>
       </c>
-      <c r="AD293" t="n">
-        <v>21113</v>
-      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -23718,9 +23649,6 @@
           <t>Semi &amp; 10km de Bordeaux</t>
         </is>
       </c>
-      <c r="AD294" t="n">
-        <v>21113</v>
-      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -24693,9 +24621,6 @@
           <t>Tout Rennes Court</t>
         </is>
       </c>
-      <c r="AD335" t="n">
-        <v>16936</v>
-      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -24718,9 +24643,6 @@
           <t>Tout Rennes Court</t>
         </is>
       </c>
-      <c r="AD336" t="n">
-        <v>16936</v>
-      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -24743,9 +24665,6 @@
           <t>Tout Rennes Court</t>
         </is>
       </c>
-      <c r="AD337" t="n">
-        <v>16936</v>
-      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -25211,9 +25130,6 @@
           <t>Marathon des Alpes-Maritimes Nice-Cannes by Kiprun</t>
         </is>
       </c>
-      <c r="AD356" t="n">
-        <v>16285</v>
-      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -25236,9 +25152,6 @@
           <t>Marathon des Alpes-Maritimes Nice-Cannes by Kiprun</t>
         </is>
       </c>
-      <c r="AD357" t="n">
-        <v>16285</v>
-      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -25366,9 +25279,6 @@
           <t>Marathon International inDeauville</t>
         </is>
       </c>
-      <c r="AD362" t="n">
-        <v>16019</v>
-      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -25391,9 +25301,6 @@
           <t>Marathon International inDeauville</t>
         </is>
       </c>
-      <c r="AD363" t="n">
-        <v>16019</v>
-      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -25416,9 +25323,6 @@
           <t>Marathon International inDeauville</t>
         </is>
       </c>
-      <c r="AD364" t="n">
-        <v>16019</v>
-      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -26456,9 +26360,6 @@
           <t>Marathon de la Liberté - Normandy Running Festival</t>
         </is>
       </c>
-      <c r="AD407" t="n">
-        <v>13798</v>
-      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -26481,9 +26382,6 @@
           <t>Marathon de la Liberté - Normandy Running Festival</t>
         </is>
       </c>
-      <c r="AD408" t="n">
-        <v>13798</v>
-      </c>
       <c r="AE408" t="n">
         <v>5138</v>
       </c>
@@ -26509,9 +26407,6 @@
           <t>Marathon de la Liberté - Normandy Running Festival</t>
         </is>
       </c>
-      <c r="AD409" t="n">
-        <v>13798</v>
-      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -26534,9 +26429,6 @@
           <t>Marathon de la Liberté - Normandy Running Festival</t>
         </is>
       </c>
-      <c r="AD410" t="n">
-        <v>13798</v>
-      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -26959,9 +26851,6 @@
           <t>Nice Semi-Marathon International</t>
         </is>
       </c>
-      <c r="AD427" t="n">
-        <v>13551</v>
-      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -26984,9 +26873,6 @@
           <t>Nice Semi-Marathon International</t>
         </is>
       </c>
-      <c r="AD428" t="n">
-        <v>13551</v>
-      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -27078,9 +26964,6 @@
           <t>La Parisienne</t>
         </is>
       </c>
-      <c r="AD432" t="n">
-        <v>13483</v>
-      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -27103,9 +26986,6 @@
           <t>La Parisienne</t>
         </is>
       </c>
-      <c r="AD433" t="n">
-        <v>13483</v>
-      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -27482,9 +27362,6 @@
           <t>Marathon International de la Côte d’Amour Amarris</t>
         </is>
       </c>
-      <c r="AD449" t="n">
-        <v>13187</v>
-      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -27507,9 +27384,6 @@
           <t>Marathon International de la Côte d’Amour Amarris</t>
         </is>
       </c>
-      <c r="AD450" t="n">
-        <v>13187</v>
-      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -27532,9 +27406,6 @@
           <t>Marathon International de la Côte d’Amour Amarris</t>
         </is>
       </c>
-      <c r="AD451" t="n">
-        <v>13187</v>
-      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -27557,9 +27428,6 @@
           <t>Marathon International de la Côte d’Amour Amarris</t>
         </is>
       </c>
-      <c r="AD452" t="n">
-        <v>13187</v>
-      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -27651,9 +27519,6 @@
           <t>Midwintern Marathon</t>
         </is>
       </c>
-      <c r="AD456" t="n">
-        <v>12766</v>
-      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -27676,9 +27541,6 @@
           <t>Midwintern Marathon</t>
         </is>
       </c>
-      <c r="AD457" t="n">
-        <v>12766</v>
-      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -27993,9 +27855,6 @@
           <t>Marathon de La Rochelle Serge Vigot</t>
         </is>
       </c>
-      <c r="AD471" t="n">
-        <v>12316</v>
-      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -28018,9 +27877,6 @@
           <t>Marathon de La Rochelle Serge Vigot</t>
         </is>
       </c>
-      <c r="AD472" t="n">
-        <v>12316</v>
-      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -29369,9 +29225,6 @@
           <t>Brooks Marathon du Lac d’Annecy</t>
         </is>
       </c>
-      <c r="AD530" t="n">
-        <v>11020</v>
-      </c>
       <c r="AE530" t="n">
         <v>5232</v>
       </c>
@@ -30177,9 +30030,6 @@
           <t>La Corrida Crédit Agricole Toulouse</t>
         </is>
       </c>
-      <c r="AD564" t="n">
-        <v>10377</v>
-      </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -30202,9 +30052,6 @@
           <t>La Corrida Crédit Agricole Toulouse</t>
         </is>
       </c>
-      <c r="AD565" t="n">
-        <v>10377</v>
-      </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -30227,9 +30074,6 @@
           <t>Montpellier Run Festival</t>
         </is>
       </c>
-      <c r="AD566" t="n">
-        <v>10313</v>
-      </c>
       <c r="AE566" t="n">
         <v>1115</v>
       </c>
@@ -30255,9 +30099,6 @@
           <t>Montpellier Run Festival</t>
         </is>
       </c>
-      <c r="AD567" t="n">
-        <v>10313</v>
-      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -30280,9 +30121,6 @@
           <t>Montpellier Run Festival</t>
         </is>
       </c>
-      <c r="AD568" t="n">
-        <v>10313</v>
-      </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -30446,9 +30284,6 @@
           <t>La Grande Course RATP du Grand Paris</t>
         </is>
       </c>
-      <c r="AD575" t="n">
-        <v>10118</v>
-      </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -30471,9 +30306,6 @@
           <t>La Grande Course RATP du Grand Paris</t>
         </is>
       </c>
-      <c r="AD576" t="n">
-        <v>10118</v>
-      </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -30496,9 +30328,6 @@
           <t>La Grande Course RATP du Grand Paris</t>
         </is>
       </c>
-      <c r="AD577" t="n">
-        <v>10118</v>
-      </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -32771,9 +32600,6 @@
           <t>Belfast City Marathon</t>
         </is>
       </c>
-      <c r="AD675" t="n">
-        <v>7827</v>
-      </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
@@ -32796,9 +32622,6 @@
           <t>Belfast City Marathon</t>
         </is>
       </c>
-      <c r="AD676" t="n">
-        <v>7827</v>
-      </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
@@ -34431,9 +34254,6 @@
           <t>Around the Bay Road Race</t>
         </is>
       </c>
-      <c r="AD748" t="n">
-        <v>6803</v>
-      </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
@@ -34456,9 +34276,6 @@
           <t>Around the Bay Road Race</t>
         </is>
       </c>
-      <c r="AD749" t="n">
-        <v>6803</v>
-      </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
@@ -36157,9 +35974,6 @@
           <t>20km de Genève</t>
         </is>
       </c>
-      <c r="AD823" t="n">
-        <v>5991</v>
-      </c>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
@@ -36182,9 +35996,6 @@
           <t>20km de Genève</t>
         </is>
       </c>
-      <c r="AD824" t="n">
-        <v>5991</v>
-      </c>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
@@ -36587,9 +36398,6 @@
           <t>Marathon des Grands Crus</t>
         </is>
       </c>
-      <c r="AD842" t="n">
-        <v>3240</v>
-      </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
@@ -36612,9 +36420,6 @@
           <t>Marathon des Grands Crus</t>
         </is>
       </c>
-      <c r="AD843" t="n">
-        <v>3240</v>
-      </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
@@ -36907,9 +36712,6 @@
           <t>Romeo &amp; Giuletta Run Half marathon</t>
         </is>
       </c>
-      <c r="AD856" t="n">
-        <v>5395</v>
-      </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
@@ -36932,9 +36734,6 @@
           <t>Romeo &amp; Giuletta Run Half marathon</t>
         </is>
       </c>
-      <c r="AD857" t="n">
-        <v>5395</v>
-      </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
@@ -40385,9 +40184,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1004" t="n">
-        <v>3915</v>
-      </c>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
@@ -40415,9 +40211,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1005" t="n">
-        <v>3915</v>
-      </c>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
@@ -40682,9 +40475,6 @@
           <t>Drammen 10K</t>
         </is>
       </c>
-      <c r="AD1017" t="n">
-        <v>3716</v>
-      </c>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
@@ -40707,9 +40497,6 @@
           <t>Drammen 10K</t>
         </is>
       </c>
-      <c r="AD1018" t="n">
-        <v>3716</v>
-      </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
@@ -43361,9 +43148,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1135" t="n">
-        <v>2558</v>
-      </c>
     </row>
     <row r="1136">
       <c r="A1136" t="inlineStr">
@@ -43391,9 +43175,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1136" t="n">
-        <v>2558</v>
-      </c>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
@@ -43713,9 +43494,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1150" t="n">
-        <v>2490</v>
-      </c>
     </row>
     <row r="1151">
       <c r="A1151" t="inlineStr">
@@ -43743,9 +43521,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1151" t="n">
-        <v>2490</v>
-      </c>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
@@ -44231,9 +44006,6 @@
           <t>Huy Night Run</t>
         </is>
       </c>
-      <c r="AD1172" t="n">
-        <v>2349</v>
-      </c>
     </row>
     <row r="1173">
       <c r="A1173" t="inlineStr">
@@ -44256,9 +44028,6 @@
           <t>Huy Night Run</t>
         </is>
       </c>
-      <c r="AD1173" t="n">
-        <v>2349</v>
-      </c>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
@@ -44925,9 +44694,6 @@
           <t>Maratona Maga Circe</t>
         </is>
       </c>
-      <c r="AD1201" t="n">
-        <v>1963</v>
-      </c>
     </row>
     <row r="1202">
       <c r="A1202" t="inlineStr">
@@ -44950,9 +44716,6 @@
           <t>Maratona Maga Circe</t>
         </is>
       </c>
-      <c r="AD1202" t="n">
-        <v>1963</v>
-      </c>
     </row>
     <row r="1203">
       <c r="A1203" t="inlineStr">
@@ -46442,9 +46205,6 @@
           <t>Santa Barbara Wine Country Half</t>
         </is>
       </c>
-      <c r="AD1267" t="n">
-        <v>1623</v>
-      </c>
     </row>
     <row r="1268">
       <c r="A1268" t="inlineStr">
@@ -46467,9 +46227,6 @@
           <t>Santa Barbara Wine Country Half</t>
         </is>
       </c>
-      <c r="AD1268" t="n">
-        <v>1623</v>
-      </c>
     </row>
     <row r="1269">
       <c r="A1269" t="inlineStr">
@@ -47118,9 +46875,6 @@
           <t>The Amazing Northampton run</t>
         </is>
       </c>
-      <c r="AD1295" t="n">
-        <v>1391</v>
-      </c>
     </row>
     <row r="1296">
       <c r="A1296" t="inlineStr">
@@ -47143,9 +46897,6 @@
           <t>The Amazing Northampton run</t>
         </is>
       </c>
-      <c r="AD1296" t="n">
-        <v>1391</v>
-      </c>
     </row>
     <row r="1297">
       <c r="A1297" t="inlineStr">
@@ -47467,9 +47218,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1309" t="n">
-        <v>1337</v>
-      </c>
     </row>
     <row r="1310">
       <c r="A1310" t="inlineStr">
@@ -47497,9 +47245,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1310" t="n">
-        <v>1337</v>
-      </c>
     </row>
     <row r="1311">
       <c r="A1311" t="inlineStr">
@@ -48221,9 +47966,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1341" t="n">
-        <v>1245</v>
-      </c>
     </row>
     <row r="1342">
       <c r="A1342" t="inlineStr">
@@ -48250,9 +47992,6 @@
         <is>
           <t>★</t>
         </is>
-      </c>
-      <c r="AD1342" t="n">
-        <v>1245</v>
       </c>
     </row>
     <row r="1343">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -3463,6 +3463,12 @@
           <t>Bank of America Chicago Marathon</t>
         </is>
       </c>
+      <c r="H25" t="n">
+        <v>33033</v>
+      </c>
+      <c r="I25" t="n">
+        <v>32995</v>
+      </c>
       <c r="Z25" t="n">
         <v>48155</v>
       </c>
@@ -3494,9 +3500,6 @@
       </c>
       <c r="AA26" t="n">
         <v>5720</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>9600</v>
       </c>
     </row>
     <row r="27">
@@ -11321,10 +11324,10 @@
         <v>32395</v>
       </c>
       <c r="I84" t="n">
-        <v>33125</v>
+        <v>33033</v>
       </c>
       <c r="J84" t="n">
-        <v>33125</v>
+        <v>32995</v>
       </c>
       <c r="K84" t="n">
         <v>33618</v>
@@ -13052,12 +13055,6 @@
       <c r="AB101" t="n">
         <v>4847</v>
       </c>
-      <c r="AC101" t="n">
-        <v>9600</v>
-      </c>
-      <c r="AD101" t="n">
-        <v>9600</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -13130,7 +13127,7 @@
         <v>6567</v>
       </c>
       <c r="AC102" t="n">
-        <v>7635</v>
+        <v>7255</v>
       </c>
       <c r="AD102" t="n">
         <v>7635</v>
@@ -21165,7 +21162,7 @@
         <v>846</v>
       </c>
       <c r="X193" t="n">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="Y193" t="inlineStr">
         <is>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -7145,6 +7145,9 @@
       <c r="AC40" t="n">
         <v>34990</v>
       </c>
+      <c r="AD40" t="n">
+        <v>39385</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -13845,7 +13845,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Göteborgsvarvet </t>
+          <t>Göteborgsvarvet</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -16216,7 +16216,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyundai Meia Maratona </t>
+          <t>Hyundai Meia Maratona</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -27676,7 +27676,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Irish Life Dublin Marathon</t>
+          <t>Irish Life Dublin Marathon</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -41312,7 +41312,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Göteborgsvarvet </t>
+          <t>Göteborgsvarvet</t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -44881,7 +44881,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Irish Life Dublin Marathon</t>
+          <t>Irish Life Dublin Marathon</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -45939,7 +45939,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyundai Meia Maratona </t>
+          <t>Hyundai Meia Maratona</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -94454,7 +94454,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Göteborgsvarvet </t>
+          <t>Göteborgsvarvet</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -14907,6 +14907,9 @@
       <c r="AC42" t="n">
         <v>31440</v>
       </c>
+      <c r="AD42" t="n">
+        <v>43779</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -43664,6 +43667,9 @@
       <c r="AD78" t="n">
         <v>31440</v>
       </c>
+      <c r="AE78" t="n">
+        <v>43779</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -14908,7 +14908,7 @@
         <v>31440</v>
       </c>
       <c r="AD42" t="n">
-        <v>43779</v>
+        <v>39473</v>
       </c>
     </row>
     <row r="43">
@@ -43668,7 +43668,7 @@
         <v>31440</v>
       </c>
       <c r="AE78" t="n">
-        <v>43779</v>
+        <v>39473</v>
       </c>
     </row>
     <row r="79">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -54514,6 +54514,9 @@
       <c r="AD211" t="n">
         <v>41616</v>
       </c>
+      <c r="AE211" t="n">
+        <v>40862</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -44363,6 +44363,9 @@
       <c r="AD85" t="n">
         <v>28990</v>
       </c>
+      <c r="AE85" t="n">
+        <v>30085</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -27311,6 +27311,9 @@
       <c r="AC22" t="n">
         <v>48361</v>
       </c>
+      <c r="AD22" t="n">
+        <v>50084</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -27576,6 +27579,9 @@
       </c>
       <c r="AC25" t="n">
         <v>28990</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>30085</v>
       </c>
     </row>
     <row r="26">
@@ -43467,6 +43473,9 @@
       <c r="AD76" t="n">
         <v>48361</v>
       </c>
+      <c r="AE76" t="n">
+        <v>50084</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -12792,7 +12792,7 @@
         <v>34734</v>
       </c>
       <c r="AD16" t="n">
-        <v>36587</v>
+        <v>36642</v>
       </c>
     </row>
     <row r="17">
@@ -27312,7 +27312,7 @@
         <v>48361</v>
       </c>
       <c r="AD22" t="n">
-        <v>50084</v>
+        <v>50071</v>
       </c>
     </row>
     <row r="23">
@@ -38761,7 +38761,7 @@
         <v>34734</v>
       </c>
       <c r="AE24" t="n">
-        <v>36587</v>
+        <v>36642</v>
       </c>
     </row>
     <row r="25">
@@ -43474,7 +43474,7 @@
         <v>48361</v>
       </c>
       <c r="AE76" t="n">
-        <v>50084</v>
+        <v>50071</v>
       </c>
     </row>
     <row r="77">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -30763,6 +30763,9 @@
       <c r="AC64" t="n">
         <v>18839</v>
       </c>
+      <c r="AD64" t="n">
+        <v>18926</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -50930,6 +50933,9 @@
       <c r="AD160" t="n">
         <v>18839</v>
       </c>
+      <c r="AE160" t="n">
+        <v>18926</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -26761,7 +26761,7 @@
         <v>9286</v>
       </c>
       <c r="AD16" t="n">
-        <v>8645</v>
+        <v>8667</v>
       </c>
     </row>
     <row r="17">
@@ -30574,7 +30574,7 @@
         <v>11671</v>
       </c>
       <c r="AD62" t="n">
-        <v>15550</v>
+        <v>15521</v>
       </c>
     </row>
     <row r="63">
@@ -32429,7 +32429,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>14049</v>
+        <v>14057</v>
       </c>
     </row>
     <row r="106">
@@ -41187,7 +41187,7 @@
         <v>9286</v>
       </c>
       <c r="AE53" t="n">
-        <v>8645</v>
+        <v>8667</v>
       </c>
     </row>
     <row r="54">
@@ -50734,7 +50734,7 @@
         <v>11671</v>
       </c>
       <c r="AE158" t="n">
-        <v>15550</v>
+        <v>15521</v>
       </c>
     </row>
     <row r="159">
@@ -58069,7 +58069,7 @@
         </is>
       </c>
       <c r="AE358" t="n">
-        <v>14049</v>
+        <v>14057</v>
       </c>
     </row>
     <row r="359">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -26198,7 +26198,7 @@
         <v>56640</v>
       </c>
       <c r="AD10" t="n">
-        <v>59830</v>
+        <v>59862</v>
       </c>
     </row>
     <row r="11">
@@ -39859,7 +39859,7 @@
         <v>56640</v>
       </c>
       <c r="AE38" t="n">
-        <v>59830</v>
+        <v>59862</v>
       </c>
     </row>
     <row r="39">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -26298,7 +26298,7 @@
         <v>55499</v>
       </c>
       <c r="AD11" t="n">
-        <v>57464</v>
+        <v>57516</v>
       </c>
     </row>
     <row r="12">
@@ -28715,13 +28715,16 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>16750</v>
+        <v>2620</v>
       </c>
       <c r="AA38" t="n">
-        <v>23636</v>
+        <v>3005</v>
       </c>
       <c r="AB38" t="n">
-        <v>19748</v>
+        <v>3593</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3786</v>
       </c>
       <c r="AD38" t="n">
         <v>5026</v>
@@ -39964,7 +39967,7 @@
         <v>55499</v>
       </c>
       <c r="AE39" t="n">
-        <v>57464</v>
+        <v>57516</v>
       </c>
     </row>
     <row r="40">
@@ -47961,13 +47964,16 @@
         </is>
       </c>
       <c r="AA124" t="n">
-        <v>16750</v>
+        <v>2620</v>
       </c>
       <c r="AB124" t="n">
-        <v>23636</v>
+        <v>3005</v>
       </c>
       <c r="AC124" t="n">
-        <v>19748</v>
+        <v>3593</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>3786</v>
       </c>
       <c r="AE124" t="n">
         <v>5026</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -28695,15 +28695,6 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T38" t="n">
-        <v>14132</v>
-      </c>
-      <c r="V38" t="n">
-        <v>21135</v>
-      </c>
-      <c r="W38" t="n">
-        <v>20140</v>
-      </c>
       <c r="X38" t="inlineStr">
         <is>
           <t>-</t>
@@ -47944,15 +47935,6 @@
           <t>x</t>
         </is>
       </c>
-      <c r="U124" t="n">
-        <v>14132</v>
-      </c>
-      <c r="W124" t="n">
-        <v>21135</v>
-      </c>
-      <c r="X124" t="n">
-        <v>20140</v>
-      </c>
       <c r="Y124" t="inlineStr">
         <is>
           <t>-</t>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -1012,10 +1012,10 @@
         <v>11787</v>
       </c>
       <c r="Z5" t="n">
-        <v>16081</v>
+        <v>16053</v>
       </c>
       <c r="AA5" t="n">
-        <v>22336</v>
+        <v>22325</v>
       </c>
       <c r="AB5" t="n">
         <v>26744</v>
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>28007</v>
+        <v>27997</v>
       </c>
       <c r="AA10" t="n">
         <v>35639</v>
@@ -1932,13 +1932,13 @@
         <v>34841</v>
       </c>
       <c r="AA15" t="n">
-        <v>41806</v>
+        <v>37497</v>
       </c>
       <c r="AB15" t="n">
-        <v>43404</v>
+        <v>43337</v>
       </c>
       <c r="AC15" t="n">
-        <v>43654</v>
+        <v>43528</v>
       </c>
       <c r="AD15" t="n">
         <v>45299</v>
@@ -27572,17 +27572,14 @@
         <v>11256</v>
       </c>
       <c r="AA25" t="n">
-        <v>13670</v>
+        <v>13727</v>
       </c>
       <c r="AB25" t="n">
-        <v>15632</v>
+        <v>16168</v>
       </c>
       <c r="AC25" t="n">
         <v>28990</v>
       </c>
-      <c r="AD25" t="n">
-        <v>30085</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -28522,16 +28519,16 @@
         <v>1689</v>
       </c>
       <c r="Z36" t="n">
-        <v>2578</v>
+        <v>2577</v>
       </c>
       <c r="AA36" t="n">
-        <v>4489</v>
+        <v>4498</v>
       </c>
       <c r="AB36" t="n">
-        <v>4057</v>
+        <v>4076</v>
       </c>
       <c r="AC36" t="n">
-        <v>4699</v>
+        <v>4710</v>
       </c>
       <c r="AD36" t="n">
         <v>5279</v>
@@ -38845,10 +38842,10 @@
         <v>11787</v>
       </c>
       <c r="AA25" t="n">
-        <v>16081</v>
+        <v>16053</v>
       </c>
       <c r="AB25" t="n">
-        <v>22336</v>
+        <v>22325</v>
       </c>
       <c r="AC25" t="n">
         <v>26744</v>
@@ -41442,7 +41439,7 @@
         </is>
       </c>
       <c r="AA56" t="n">
-        <v>28007</v>
+        <v>27997</v>
       </c>
       <c r="AB56" t="n">
         <v>35639</v>
@@ -42947,13 +42944,13 @@
         <v>34841</v>
       </c>
       <c r="AB70" t="n">
-        <v>41806</v>
+        <v>37497</v>
       </c>
       <c r="AC70" t="n">
-        <v>43404</v>
+        <v>43337</v>
       </c>
       <c r="AD70" t="n">
-        <v>43654</v>
+        <v>43528</v>
       </c>
       <c r="AE70" t="n">
         <v>45299</v>
@@ -44361,17 +44358,14 @@
         <v>11256</v>
       </c>
       <c r="AB85" t="n">
-        <v>13670</v>
+        <v>13727</v>
       </c>
       <c r="AC85" t="n">
-        <v>15632</v>
+        <v>16168</v>
       </c>
       <c r="AD85" t="n">
         <v>28990</v>
       </c>
-      <c r="AE85" t="n">
-        <v>30085</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -47453,16 +47447,16 @@
         </is>
       </c>
       <c r="AA118" t="n">
-        <v>20474</v>
+        <v>20472</v>
       </c>
       <c r="AB118" t="n">
         <v>28025</v>
       </c>
       <c r="AC118" t="n">
-        <v>31455</v>
+        <v>31445</v>
       </c>
       <c r="AD118" t="n">
-        <v>33050</v>
+        <v>33048</v>
       </c>
       <c r="AE118" t="n">
         <v>34003</v>
@@ -47555,16 +47549,16 @@
         <v>1689</v>
       </c>
       <c r="AA119" t="n">
-        <v>2578</v>
+        <v>2577</v>
       </c>
       <c r="AB119" t="n">
-        <v>4489</v>
+        <v>4498</v>
       </c>
       <c r="AC119" t="n">
-        <v>4057</v>
+        <v>4076</v>
       </c>
       <c r="AD119" t="n">
-        <v>4699</v>
+        <v>4710</v>
       </c>
       <c r="AE119" t="n">
         <v>5279</v>
@@ -47635,14 +47629,11 @@
         <v>25773</v>
       </c>
       <c r="AC120" t="n">
-        <v>27897</v>
+        <v>27883</v>
       </c>
       <c r="AD120" t="n">
         <v>30049</v>
       </c>
-      <c r="AE120" t="n">
-        <v>27883</v>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -48284,16 +48275,16 @@
         </is>
       </c>
       <c r="AA128" t="n">
-        <v>16782</v>
+        <v>12559</v>
       </c>
       <c r="AB128" t="n">
         <v>11858</v>
       </c>
       <c r="AC128" t="n">
-        <v>16010</v>
+        <v>14150</v>
       </c>
       <c r="AD128" t="n">
-        <v>20007</v>
+        <v>16853</v>
       </c>
       <c r="AE128" t="n">
         <v>19814</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -27578,7 +27578,7 @@
         <v>16168</v>
       </c>
       <c r="AC25" t="n">
-        <v>28990</v>
+        <v>30085</v>
       </c>
     </row>
     <row r="26">
@@ -44364,7 +44364,7 @@
         <v>16168</v>
       </c>
       <c r="AD85" t="n">
-        <v>28990</v>
+        <v>30085</v>
       </c>
     </row>
     <row r="86">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -45135,6 +45135,9 @@
       <c r="AD92" t="n">
         <v>16280</v>
       </c>
+      <c r="AE92" t="n">
+        <v>15862</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -45771,6 +45774,9 @@
       <c r="AD99" t="n">
         <v>11338</v>
       </c>
+      <c r="AE99" t="n">
+        <v>10051</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -50836,6 +50842,9 @@
       <c r="AD159" t="n">
         <v>12319</v>
       </c>
+      <c r="AE159" t="n">
+        <v>12327</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -53796,6 +53805,9 @@
       </c>
       <c r="AD190" t="n">
         <v>5145</v>
+      </c>
+      <c r="AE190" t="n">
+        <v>5591</v>
       </c>
     </row>
     <row r="191">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -2383,6 +2383,9 @@
       <c r="AC19" t="n">
         <v>11338</v>
       </c>
+      <c r="AD19" t="n">
+        <v>10051</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -12119,7 +12122,7 @@
         <v>22872</v>
       </c>
       <c r="AD7" t="n">
-        <v>22475</v>
+        <v>23645</v>
       </c>
     </row>
     <row r="8">
@@ -13582,7 +13585,7 @@
         <v>19968</v>
       </c>
       <c r="AD26" t="n">
-        <v>23383</v>
+        <v>19754</v>
       </c>
     </row>
     <row r="27">
@@ -15598,6 +15601,9 @@
       </c>
       <c r="AC49" t="n">
         <v>16280</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>15862</v>
       </c>
     </row>
     <row r="50">
@@ -27344,7 +27350,7 @@
         <v>48361</v>
       </c>
       <c r="AD22" t="n">
-        <v>50071</v>
+        <v>50083</v>
       </c>
     </row>
     <row r="23">
@@ -31899,6 +31905,9 @@
       </c>
       <c r="AC77" t="n">
         <v>5145</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>5591</v>
       </c>
     </row>
     <row r="78">
@@ -37666,7 +37675,7 @@
         <v>22872</v>
       </c>
       <c r="AE11" t="n">
-        <v>22475</v>
+        <v>23645</v>
       </c>
     </row>
     <row r="12">
@@ -40506,7 +40515,7 @@
         <v>19968</v>
       </c>
       <c r="AE44" t="n">
-        <v>23383</v>
+        <v>19754</v>
       </c>
     </row>
     <row r="45">
@@ -43500,7 +43509,7 @@
         <v>48361</v>
       </c>
       <c r="AE76" t="n">
-        <v>50071</v>
+        <v>50083</v>
       </c>
     </row>
     <row r="77">
@@ -50841,9 +50850,6 @@
       </c>
       <c r="AD159" t="n">
         <v>12319</v>
-      </c>
-      <c r="AE159" t="n">
-        <v>12327</v>
       </c>
     </row>
     <row r="160">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -1467,10 +1467,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Y11" t="n">
+        <v>6325</v>
       </c>
       <c r="Z11" t="n">
         <v>10863</v>
@@ -3007,10 +3005,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Y27" t="n">
+        <v>2851</v>
       </c>
       <c r="Z27" t="n">
         <v>4672</v>
@@ -14383,7 +14379,7 @@
         </is>
       </c>
       <c r="Y36" t="n">
-        <v>2495</v>
+        <v>2462</v>
       </c>
       <c r="Z36" t="n">
         <v>5394</v>
@@ -14437,7 +14433,7 @@
         </is>
       </c>
       <c r="Y37" t="n">
-        <v>5947</v>
+        <v>4082</v>
       </c>
       <c r="Z37" t="n">
         <v>5507</v>
@@ -14782,7 +14778,7 @@
         </is>
       </c>
       <c r="Y41" t="n">
-        <v>49623</v>
+        <v>30454</v>
       </c>
       <c r="Z41" t="n">
         <v>41066</v>
@@ -26515,7 +26511,7 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>13857</v>
+        <v>11818</v>
       </c>
       <c r="Z13" t="n">
         <v>14184</v>
@@ -40366,7 +40362,7 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>13857</v>
+        <v>11818</v>
       </c>
       <c r="AA43" t="n">
         <v>14184</v>
@@ -42056,10 +42052,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Z62" t="n">
+        <v>6325</v>
       </c>
       <c r="AA62" t="n">
         <v>10863</v>
@@ -42195,7 +42189,7 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>2495</v>
+        <v>2462</v>
       </c>
       <c r="AA63" t="n">
         <v>5394</v>
@@ -42254,7 +42248,7 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>5947</v>
+        <v>4082</v>
       </c>
       <c r="AA64" t="n">
         <v>5507</v>
@@ -43578,7 +43572,7 @@
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>49623</v>
+        <v>30454</v>
       </c>
       <c r="AA77" t="n">
         <v>41066</v>
@@ -51390,6 +51384,9 @@
       <c r="AD166" t="n">
         <v>37233</v>
       </c>
+      <c r="AE166" t="n">
+        <v>37133</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -51973,10 +51970,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Z172" t="n">
+        <v>2851</v>
       </c>
       <c r="AA172" t="n">
         <v>4672</v>
@@ -52095,7 +52090,7 @@
         </is>
       </c>
       <c r="Z174" t="n">
-        <v>15567</v>
+        <v>11300</v>
       </c>
       <c r="AA174" t="n">
         <v>13062</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -31673,6 +31673,9 @@
       <c r="AB75" t="n">
         <v>1475</v>
       </c>
+      <c r="AD75" t="n">
+        <v>1869</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -33604,6 +33607,9 @@
       </c>
       <c r="AC166" t="n">
         <v>8221</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>8051</v>
       </c>
     </row>
     <row r="167">
@@ -53336,6 +53342,9 @@
       <c r="AC186" t="n">
         <v>1475</v>
       </c>
+      <c r="AE186" t="n">
+        <v>1869</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -65327,6 +65336,9 @@
       </c>
       <c r="AD667" t="n">
         <v>8221</v>
+      </c>
+      <c r="AE667" t="n">
+        <v>8051</v>
       </c>
     </row>
     <row r="668">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -52895,6 +52895,9 @@
       <c r="AD182" t="n">
         <v>28985</v>
       </c>
+      <c r="AE182" t="n">
+        <v>29102</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -44303,6 +44303,9 @@
       <c r="AD84" t="n">
         <v>54187</v>
       </c>
+      <c r="AE84" t="n">
+        <v>54581</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -27515,6 +27515,9 @@
       <c r="AC24" t="n">
         <v>54187</v>
       </c>
+      <c r="AD24" t="n">
+        <v>54581</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -15218,6 +15218,9 @@
       <c r="AC46" t="n">
         <v>24634</v>
       </c>
+      <c r="AD46" t="n">
+        <v>24038</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -15335,6 +15338,9 @@
       <c r="AC47" t="n">
         <v>22376</v>
       </c>
+      <c r="AD47" t="n">
+        <v>22918</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -15678,6 +15684,9 @@
       <c r="AC50" t="n">
         <v>16201</v>
       </c>
+      <c r="AD50" t="n">
+        <v>17289</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -15909,6 +15918,9 @@
       </c>
       <c r="AC52" t="n">
         <v>13341</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>12778</v>
       </c>
     </row>
     <row r="53">
@@ -27704,6 +27716,9 @@
       </c>
       <c r="AC26" t="n">
         <v>23326</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>23635</v>
       </c>
     </row>
     <row r="27">
@@ -44558,6 +44573,9 @@
       <c r="AD87" t="n">
         <v>24634</v>
       </c>
+      <c r="AE87" t="n">
+        <v>24038</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -44651,6 +44669,9 @@
       <c r="AD88" t="n">
         <v>23326</v>
       </c>
+      <c r="AE88" t="n">
+        <v>23635</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -44773,6 +44794,9 @@
       <c r="AD89" t="n">
         <v>22376</v>
       </c>
+      <c r="AE89" t="n">
+        <v>22918</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -45235,6 +45259,9 @@
       <c r="AD93" t="n">
         <v>16201</v>
       </c>
+      <c r="AE93" t="n">
+        <v>17289</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -45476,6 +45503,9 @@
       </c>
       <c r="AD95" t="n">
         <v>13341</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>12778</v>
       </c>
     </row>
     <row r="96">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -15936,7 +15936,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Nike Melbourne Marathon Festival</t>
+          <t>Nike Half Marathon</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -16002,6 +16002,9 @@
       </c>
       <c r="AC53" t="n">
         <v>12156</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>13905</v>
       </c>
     </row>
     <row r="54">
@@ -25443,7 +25446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD339"/>
+  <dimension ref="A1:AD340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36711,6 +36714,26 @@
       </c>
       <c r="AD339" t="n">
         <v>30581</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Nike Melbourne Marathon</t>
+        </is>
+      </c>
+      <c r="AD340" t="n">
+        <v>17732</v>
       </c>
     </row>
   </sheetData>
@@ -36724,7 +36747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1935"/>
+  <dimension ref="A1:AE1936"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="18.21875" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -45526,7 +45549,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Nike Melbourne Marathon Festival</t>
+          <t>Nike Half Marathon</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -45593,6 +45616,9 @@
       <c r="AD96" t="n">
         <v>12156</v>
       </c>
+      <c r="AE96" t="n">
+        <v>13905</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -94124,6 +94150,31 @@
       </c>
       <c r="AE1935" t="n">
         <v>28635</v>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B1936" t="inlineStr">
+        <is>
+          <t>Melbourne</t>
+        </is>
+      </c>
+      <c r="C1936" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D1936" t="inlineStr">
+        <is>
+          <t>Nike Melbourne Marathon</t>
+        </is>
+      </c>
+      <c r="AE1936" t="n">
+        <v>17732</v>
       </c>
     </row>
   </sheetData>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -15936,7 +15936,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Nike Half Marathon</t>
+          <t>Nike Melbourne Half Marathon</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -45549,7 +45549,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Nike Half Marathon</t>
+          <t>Nike Melbourne Half Marathon</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -16294,6 +16294,9 @@
       <c r="AC57" t="n">
         <v>7635</v>
       </c>
+      <c r="AD57" t="n">
+        <v>8219</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -27876,6 +27879,9 @@
       </c>
       <c r="AB28" t="n">
         <v>5692</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>8297</v>
       </c>
     </row>
     <row r="29">
@@ -46038,6 +46044,9 @@
       <c r="AC101" t="n">
         <v>5692</v>
       </c>
+      <c r="AE101" t="n">
+        <v>8297</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -46114,6 +46123,9 @@
       </c>
       <c r="AD102" t="n">
         <v>7635</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>8219</v>
       </c>
     </row>
     <row r="103">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -26266,7 +26266,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Schneider Electric Marathon de Paris</t>
+          <t>ASICS Marathon de Paris</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -39961,7 +39961,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Schneider Electric Marathon de Paris</t>
+          <t>ASICS Marathon de Paris</t>
         </is>
       </c>
       <c r="E39" t="n">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -54584,7 +54584,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>50702</v>
+        <v>50103</v>
       </c>
     </row>
     <row r="210">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -54583,6 +54583,9 @@
           <t>Course de l'escalade</t>
         </is>
       </c>
+      <c r="AC209" t="n">
+        <v>47476</v>
+      </c>
       <c r="AD209" t="n">
         <v>50103</v>
       </c>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -54592,6 +54592,9 @@
           <t>Course de l'escalade</t>
         </is>
       </c>
+      <c r="AB209" t="n">
+        <v>46369</v>
+      </c>
       <c r="AC209" t="n">
         <v>47476</v>
       </c>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -54648,6 +54648,9 @@
           <t>20KM de Bruxelles</t>
         </is>
       </c>
+      <c r="AC211" t="n">
+        <v>43811</v>
+      </c>
       <c r="AD211" t="n">
         <v>41616</v>
       </c>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -1164,6 +1164,9 @@
       <c r="AC7" t="n">
         <v>39385</v>
       </c>
+      <c r="AD7" t="n">
+        <v>45408</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -40109,6 +40112,9 @@
       <c r="AD40" t="n">
         <v>39385</v>
       </c>
+      <c r="AE40" t="n">
+        <v>45408</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -3764,9 +3764,6 @@
           <t>Great Ethiopan Run</t>
         </is>
       </c>
-      <c r="AC44" t="n">
-        <v>45650</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7827,9 +7824,6 @@
           <t>Run the City</t>
         </is>
       </c>
-      <c r="AC268" t="n">
-        <v>2988</v>
-      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -7934,9 +7928,6 @@
         <is>
           <t>Mumbai Midnight 10K</t>
         </is>
-      </c>
-      <c r="AC274" t="n">
-        <v>2822</v>
       </c>
     </row>
     <row r="275">
@@ -19029,9 +19020,6 @@
           <t>Guadalajara Half Marathon</t>
         </is>
       </c>
-      <c r="AC163" t="n">
-        <v>9960</v>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -19066,9 +19054,6 @@
           <t>Bank of China Beijing Half Marathon</t>
         </is>
       </c>
-      <c r="AC165" t="n">
-        <v>9960</v>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -21749,9 +21734,6 @@
           <t>Middlesbrough half marathon</t>
         </is>
       </c>
-      <c r="AC315" t="n">
-        <v>2241</v>
-      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -22689,9 +22671,6 @@
           <t>Rolling Half</t>
         </is>
       </c>
-      <c r="AC366" t="n">
-        <v>1245</v>
-      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -22957,9 +22936,6 @@
         <is>
           <t>DrammenDrammen Halv Maraton</t>
         </is>
-      </c>
-      <c r="AC381" t="n">
-        <v>830</v>
       </c>
     </row>
     <row r="382">
@@ -32115,9 +32091,6 @@
           <t>Bank of China Beijing Marathon</t>
         </is>
       </c>
-      <c r="AC86" t="n">
-        <v>26560</v>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -32252,9 +32225,6 @@
           <t>Guangzhou Marathon</t>
         </is>
       </c>
-      <c r="AC93" t="n">
-        <v>21580</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -32416,9 +32386,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AC101" t="n">
-        <v>16600</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -32436,9 +32403,6 @@
           <t>Hokkaido Marathon</t>
         </is>
       </c>
-      <c r="AC102" t="n">
-        <v>16600</v>
-      </c>
       <c r="AD102" t="n">
         <v>18607</v>
       </c>
@@ -33214,9 +33178,6 @@
           <t>Fukuoka Marathon</t>
         </is>
       </c>
-      <c r="AC143" t="n">
-        <v>10790</v>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -33585,9 +33546,6 @@
           <t>Kitakyushu Marathon</t>
         </is>
       </c>
-      <c r="AC163" t="n">
-        <v>8300</v>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -34002,9 +33960,6 @@
           <t>Tokushima Marathon</t>
         </is>
       </c>
-      <c r="AC186" t="n">
-        <v>6640</v>
-      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -34271,9 +34226,6 @@
         <is>
           <t>Guadalajara Marathon</t>
         </is>
-      </c>
-      <c r="AC201" t="n">
-        <v>5810</v>
       </c>
     </row>
     <row r="202">
@@ -54629,9 +54581,6 @@
           <t>Great Ethiopan Run</t>
         </is>
       </c>
-      <c r="AD210" t="n">
-        <v>45650</v>
-      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -55487,9 +55436,6 @@
           <t>Bank of China Beijing Marathon</t>
         </is>
       </c>
-      <c r="AD246" t="n">
-        <v>26560</v>
-      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -56419,9 +56365,6 @@
           <t>Guangzhou Marathon</t>
         </is>
       </c>
-      <c r="AD284" t="n">
-        <v>21580</v>
-      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -56922,9 +56865,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD305" t="n">
-        <v>19090</v>
-      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -58028,9 +57968,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD351" t="n">
-        <v>16600</v>
-      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -58053,9 +57990,6 @@
           <t>Hokkaido Marathon</t>
         </is>
       </c>
-      <c r="AD352" t="n">
-        <v>16600</v>
-      </c>
       <c r="AE352" t="n">
         <v>18607</v>
       </c>
@@ -59305,9 +59239,6 @@
           <t>The Music Run</t>
         </is>
       </c>
-      <c r="AD404" t="n">
-        <v>14110</v>
-      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -60756,9 +60687,6 @@
           <t>JBG Kolkata Marathon</t>
         </is>
       </c>
-      <c r="AD466" t="n">
-        <v>12450</v>
-      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -62688,9 +62616,6 @@
           <t>Fukuoka Marathon</t>
         </is>
       </c>
-      <c r="AD550" t="n">
-        <v>10790</v>
-      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -63634,9 +63559,6 @@
           <t>Guadalajara Half Marathon</t>
         </is>
       </c>
-      <c r="AD590" t="n">
-        <v>9960</v>
-      </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -63703,9 +63625,6 @@
           <t>Tay Ho Half Marathon</t>
         </is>
       </c>
-      <c r="AD593" t="n">
-        <v>9960</v>
-      </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -63728,9 +63647,6 @@
           <t>Bank of China Beijing Half Marathon</t>
         </is>
       </c>
-      <c r="AD594" t="n">
-        <v>9960</v>
-      </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -64072,9 +63988,6 @@
           <t>Love Run</t>
         </is>
       </c>
-      <c r="AD608" t="n">
-        <v>9130</v>
-      </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -64989,9 +64902,6 @@
           <t>Kitakyushu Marathon</t>
         </is>
       </c>
-      <c r="AD648" t="n">
-        <v>8300</v>
-      </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -67475,9 +67385,6 @@
           <t>Tokushima Marathon</t>
         </is>
       </c>
-      <c r="AD757" t="n">
-        <v>6640</v>
-      </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
@@ -69223,9 +69130,6 @@
           <t>Guadalajara Marathon</t>
         </is>
       </c>
-      <c r="AD833" t="n">
-        <v>5810</v>
-      </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
@@ -72742,9 +72646,6 @@
           <t>Rome 15K</t>
         </is>
       </c>
-      <c r="AD984" t="n">
-        <v>4150</v>
-      </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
@@ -75033,9 +74934,6 @@
           <t>Run the City</t>
         </is>
       </c>
-      <c r="AD1085" t="n">
-        <v>2988</v>
-      </c>
     </row>
     <row r="1086">
       <c r="A1086" t="inlineStr">
@@ -75281,9 +75179,6 @@
           <t>La liégeoise Women Only</t>
         </is>
       </c>
-      <c r="AD1096" t="n">
-        <v>2905</v>
-      </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
@@ -75400,9 +75295,6 @@
           <t>Mumbai Midnight 10K</t>
         </is>
       </c>
-      <c r="AD1101" t="n">
-        <v>2822</v>
-      </c>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
@@ -77063,9 +76955,6 @@
           <t>Middlesbrough half marathon</t>
         </is>
       </c>
-      <c r="AD1173" t="n">
-        <v>2241</v>
-      </c>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
@@ -78973,9 +78862,6 @@
           <t>J.P Morgan City Jogging</t>
         </is>
       </c>
-      <c r="AD1255" t="n">
-        <v>1660</v>
-      </c>
     </row>
     <row r="1256">
       <c r="A1256" t="inlineStr">
@@ -79747,9 +79633,6 @@
           <t>La trenta trentina</t>
         </is>
       </c>
-      <c r="AD1288" t="n">
-        <v>1411</v>
-      </c>
     </row>
     <row r="1289">
       <c r="A1289" t="inlineStr">
@@ -80751,9 +80634,6 @@
           <t>Rolling Half</t>
         </is>
       </c>
-      <c r="AD1330" t="n">
-        <v>1245</v>
-      </c>
     </row>
     <row r="1331">
       <c r="A1331" t="inlineStr">
@@ -81794,9 +81674,6 @@
           <t>DrammenDrammen Halv Maraton</t>
         </is>
       </c>
-      <c r="AD1376" t="n">
-        <v>830</v>
-      </c>
     </row>
     <row r="1377">
       <c r="A1377" t="inlineStr">
@@ -81818,9 +81695,6 @@
         <is>
           <t>Terre di Siena Ultramarathon</t>
         </is>
-      </c>
-      <c r="AD1377" t="n">
-        <v>830</v>
       </c>
     </row>
     <row r="1378">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -3812,7 +3812,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>World 10K bengaluru</t>
+          <t>TCS World 10K Bengaluru</t>
         </is>
       </c>
       <c r="AC47" t="n">
@@ -54832,7 +54832,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>World 10K bengaluru</t>
+          <t>TCS World 10K Bengaluru</t>
         </is>
       </c>
       <c r="AD221" t="n">
@@ -54860,7 +54860,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>World 10K bengaluru</t>
+          <t>TCS World 10K Bengaluru</t>
         </is>
       </c>
       <c r="AD222" t="n">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -54640,6 +54640,9 @@
       <c r="AD212" t="n">
         <v>35070</v>
       </c>
+      <c r="AE212" t="n">
+        <v>35949</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -54637,6 +54637,15 @@
           <t>Baloise Antwerp 10 miles</t>
         </is>
       </c>
+      <c r="AA212" t="n">
+        <v>19977</v>
+      </c>
+      <c r="AB212" t="n">
+        <v>26686</v>
+      </c>
+      <c r="AC212" t="n">
+        <v>29233</v>
+      </c>
       <c r="AD212" t="n">
         <v>35070</v>
       </c>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hot Chocolate Run</t>
+          <t>SKECHERS Hot Chocolate Run - Philadelphia</t>
         </is>
       </c>
     </row>
@@ -54878,7 +54878,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Hot Chocolate Run</t>
+          <t>SKECHERS Hot Chocolate Run - Philadelphia</t>
         </is>
       </c>
     </row>
@@ -54900,7 +54900,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Hot Chocolate Run</t>
+          <t>SKECHERS Hot Chocolate Run - Philadelphia</t>
         </is>
       </c>
     </row>
@@ -54922,7 +54922,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Hot Chocolate Run</t>
+          <t>SKECHERS Hot Chocolate Run - Philadelphia</t>
         </is>
       </c>
       <c r="AD224" t="n">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -3841,6 +3841,9 @@
           <t>SKECHERS Hot Chocolate Run - Philadelphia</t>
         </is>
       </c>
+      <c r="AD48" t="n">
+        <v>1936</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -54881,6 +54884,9 @@
           <t>SKECHERS Hot Chocolate Run - Philadelphia</t>
         </is>
       </c>
+      <c r="AE222" t="n">
+        <v>1936</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -54903,6 +54909,9 @@
           <t>SKECHERS Hot Chocolate Run - Philadelphia</t>
         </is>
       </c>
+      <c r="AE223" t="n">
+        <v>4714</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -54925,8 +54934,8 @@
           <t>SKECHERS Hot Chocolate Run - Philadelphia</t>
         </is>
       </c>
-      <c r="AD224" t="n">
-        <v>33547</v>
+      <c r="AE224" t="n">
+        <v>1260</v>
       </c>
     </row>
     <row r="225">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -13967,9 +13967,18 @@
           <t>x</t>
         </is>
       </c>
+      <c r="R32" t="n">
+        <v>25639</v>
+      </c>
       <c r="S32" t="n">
         <v>26482</v>
       </c>
+      <c r="T32" t="n">
+        <v>27444</v>
+      </c>
+      <c r="U32" t="n">
+        <v>27445</v>
+      </c>
       <c r="W32" t="n">
         <v>26803</v>
       </c>
@@ -13982,6 +13991,15 @@
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="Z32" t="n">
+        <v>18827</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>25418</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>28442</v>
       </c>
       <c r="AC32" t="n">
         <v>28474</v>
@@ -41598,9 +41616,18 @@
           <t>x</t>
         </is>
       </c>
+      <c r="S57" t="n">
+        <v>25639</v>
+      </c>
       <c r="T57" t="n">
         <v>26482</v>
       </c>
+      <c r="U57" t="n">
+        <v>27444</v>
+      </c>
+      <c r="V57" t="n">
+        <v>27445</v>
+      </c>
       <c r="X57" t="n">
         <v>26803</v>
       </c>
@@ -41613,6 +41640,15 @@
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="AA57" t="n">
+        <v>18827</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>25418</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>28442</v>
       </c>
       <c r="AD57" t="n">
         <v>28474</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -5146,6 +5146,9 @@
       <c r="AC118" t="n">
         <v>4648</v>
       </c>
+      <c r="AD118" t="n">
+        <v>3928</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -15188,6 +15191,9 @@
       <c r="AC45" t="n">
         <v>26060</v>
       </c>
+      <c r="AD45" t="n">
+        <v>25498</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -18678,6 +18684,9 @@
       <c r="AC143" t="n">
         <v>4804</v>
       </c>
+      <c r="AD143" t="n">
+        <v>4917</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -24889,6 +24898,9 @@
       </c>
       <c r="AC493" t="n">
         <v>8900</v>
+      </c>
+      <c r="AD493" t="n">
+        <v>12260</v>
       </c>
     </row>
     <row r="494">
@@ -33114,6 +33126,9 @@
       <c r="AC138" t="n">
         <v>1853</v>
       </c>
+      <c r="AD138" t="n">
+        <v>2398</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -36430,6 +36445,9 @@
       </c>
       <c r="AC323" t="n">
         <v>2900</v>
+      </c>
+      <c r="AD323" t="n">
+        <v>15683</v>
       </c>
     </row>
     <row r="324">
@@ -44552,6 +44570,9 @@
       <c r="AD86" t="n">
         <v>26060</v>
       </c>
+      <c r="AE86" t="n">
+        <v>25498</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -61951,6 +61972,9 @@
       <c r="AD518" t="n">
         <v>1853</v>
       </c>
+      <c r="AE518" t="n">
+        <v>2398</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -61976,6 +62000,9 @@
       <c r="AD519" t="n">
         <v>4804</v>
       </c>
+      <c r="AE519" t="n">
+        <v>4917</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -62001,6 +62028,9 @@
       <c r="AD520" t="n">
         <v>4648</v>
       </c>
+      <c r="AE520" t="n">
+        <v>3928</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -91556,6 +91586,9 @@
       <c r="AD1818" t="n">
         <v>2900</v>
       </c>
+      <c r="AE1818" t="n">
+        <v>15683</v>
+      </c>
     </row>
     <row r="1819">
       <c r="A1819" t="inlineStr">
@@ -91580,6 +91613,9 @@
       </c>
       <c r="AD1819" t="n">
         <v>8900</v>
+      </c>
+      <c r="AE1819" t="n">
+        <v>12260</v>
       </c>
     </row>
     <row r="1820">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -30742,6 +30742,9 @@
       <c r="AC63" t="n">
         <v>12319</v>
       </c>
+      <c r="AD63" t="n">
+        <v>13331</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -50955,6 +50958,9 @@
       <c r="AD159" t="n">
         <v>12319</v>
       </c>
+      <c r="AE159" t="n">
+        <v>13331</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
